--- a/.pic/Other/rv32i/example_instr_code.xlsx
+++ b/.pic/Other/rv32i/example_instr_code.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\voult\Desktop\APS-reborn\.pic\Other\rv32i\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE47DEEE-8362-410D-B139-02CAD8AFDE58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{11EFC6F1-332B-4EA5-A40A-5D79FF20EEEF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,15 +25,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
-  <si>
-    <t>Код ассемблера</t>
-  </si>
-  <si>
-    <t>Значения полей</t>
-  </si>
-  <si>
-    <t>Машинный код</t>
-  </si>
   <si>
     <t>add s2, s3, s4</t>
   </si>
@@ -109,11 +94,20 @@
   <si>
     <t>(0x407302B3)</t>
   </si>
+  <si>
+    <t>Assembly code</t>
+  </si>
+  <si>
+    <t>Field values</t>
+  </si>
+  <si>
+    <t>Machine code</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -224,15 +218,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -241,7 +229,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -281,7 +275,7 @@
         <xdr:cNvPr id="3" name="Правая круглая скобка 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AD72D32-776C-4736-B66D-3CCAFD71C033}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AD72D32-776C-4736-B66D-3CCAFD71C033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -340,7 +334,7 @@
         <xdr:cNvPr id="4" name="Правая круглая скобка 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4613D476-DBFD-46EB-B0AB-B50870D03C20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4613D476-DBFD-46EB-B0AB-B50870D03C20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -399,7 +393,7 @@
         <xdr:cNvPr id="5" name="Правая круглая скобка 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CAAEAE2-7C9A-4A0F-A01F-37161E90E4E1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CAAEAE2-7C9A-4A0F-A01F-37161E90E4E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -458,7 +452,7 @@
         <xdr:cNvPr id="6" name="Правая круглая скобка 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B727BC8-F5A5-4892-9F3A-471622832A53}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5B727BC8-F5A5-4892-9F3A-471622832A53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -517,7 +511,7 @@
         <xdr:cNvPr id="7" name="Правая круглая скобка 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A3379B5-B194-4E2D-8A30-35AA3E27FF03}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2A3379B5-B194-4E2D-8A30-35AA3E27FF03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -576,7 +570,7 @@
         <xdr:cNvPr id="9" name="Правая круглая скобка 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D711405-87A4-444D-AE01-1F3708710AB4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9D711405-87A4-444D-AE01-1F3708710AB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -635,7 +629,7 @@
         <xdr:cNvPr id="10" name="Правая круглая скобка 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E2EF2-0404-459A-BCA9-0D0BD586D977}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D2E2EF2-0404-459A-BCA9-0D0BD586D977}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -694,7 +688,7 @@
         <xdr:cNvPr id="11" name="Правая круглая скобка 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072E865-8694-4852-8E9B-020338661E57}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2072E865-8694-4852-8E9B-020338661E57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -753,7 +747,7 @@
         <xdr:cNvPr id="13" name="Правая круглая скобка 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0684CE70-7DDC-4530-9AFE-2DD98F1096A5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0684CE70-7DDC-4530-9AFE-2DD98F1096A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -812,7 +806,7 @@
         <xdr:cNvPr id="14" name="Правая круглая скобка 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E8BB5D8-667B-4A9F-B14F-42853C233854}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E8BB5D8-667B-4A9F-B14F-42853C233854}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -871,7 +865,7 @@
         <xdr:cNvPr id="15" name="Правая круглая скобка 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC60ACD-2584-476E-A503-82676D64B353}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6FC60ACD-2584-476E-A503-82676D64B353}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -930,7 +924,7 @@
         <xdr:cNvPr id="16" name="Правая круглая скобка 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2AB13F0-762C-4879-AFD3-4CE2A7F213B4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E2AB13F0-762C-4879-AFD3-4CE2A7F213B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -989,7 +983,7 @@
         <xdr:cNvPr id="17" name="Правая круглая скобка 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F860691-8868-4774-B441-248AD237CFD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3F860691-8868-4774-B441-248AD237CFD2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1048,7 +1042,7 @@
         <xdr:cNvPr id="18" name="Правая круглая скобка 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F9CB1D-6C2E-44D9-B66A-4111848A6BC7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B9F9CB1D-6C2E-44D9-B66A-4111848A6BC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1107,7 +1101,7 @@
         <xdr:cNvPr id="19" name="Правая круглая скобка 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5508713C-AEAF-4B62-88AA-3653ABAD411A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5508713C-AEAF-4B62-88AA-3653ABAD411A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1166,7 +1160,7 @@
         <xdr:cNvPr id="20" name="Правая круглая скобка 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{155D0124-2059-4D4D-99E2-719AB9D8CA16}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{155D0124-2059-4D4D-99E2-719AB9D8CA16}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1225,7 +1219,7 @@
         <xdr:cNvPr id="21" name="TextBox 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D05A31-49FC-466E-BA5A-B5D0634DA844}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{56D05A31-49FC-466E-BA5A-B5D0634DA844}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1298,7 +1292,7 @@
         <xdr:cNvPr id="22" name="TextBox 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB09DC36-352C-424A-B6B8-A49A3F14C290}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FB09DC36-352C-424A-B6B8-A49A3F14C290}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,7 +1365,7 @@
         <xdr:cNvPr id="23" name="TextBox 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDFCD283-19D7-4AC1-9D14-5DD08D2C094D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CDFCD283-19D7-4AC1-9D14-5DD08D2C094D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1444,7 +1438,7 @@
         <xdr:cNvPr id="24" name="TextBox 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34889B57-E1E9-44B4-8491-F6CAF2E16A96}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{34889B57-E1E9-44B4-8491-F6CAF2E16A96}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1517,7 +1511,7 @@
         <xdr:cNvPr id="25" name="TextBox 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B1FDA8A-5ABE-460A-AC29-4D1D633C1CD4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1B1FDA8A-5ABE-460A-AC29-4D1D633C1CD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1590,7 +1584,7 @@
         <xdr:cNvPr id="26" name="TextBox 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE450EE7-CB30-4B4E-9392-A28450621293}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FE450EE7-CB30-4B4E-9392-A28450621293}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1663,7 +1657,7 @@
         <xdr:cNvPr id="27" name="TextBox 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAB4829E-DE9A-4743-B5F2-D416BF1B0AC7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BAB4829E-DE9A-4743-B5F2-D416BF1B0AC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1736,7 +1730,7 @@
         <xdr:cNvPr id="28" name="TextBox 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C630E6C-77F1-47B9-AC8E-14ECD5BD5BCB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C630E6C-77F1-47B9-AC8E-14ECD5BD5BCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1809,7 +1803,7 @@
         <xdr:cNvPr id="29" name="TextBox 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59381342-04B7-46B1-9626-D25F082ED2F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{59381342-04B7-46B1-9626-D25F082ED2F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1882,7 +1876,7 @@
         <xdr:cNvPr id="30" name="TextBox 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265F17FE-BCA8-458B-9AE4-D9337C8557C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{265F17FE-BCA8-458B-9AE4-D9337C8557C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1955,7 +1949,7 @@
         <xdr:cNvPr id="31" name="TextBox 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D452D1CC-A63D-4E5D-8484-D2C73EC183EC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D452D1CC-A63D-4E5D-8484-D2C73EC183EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2028,7 +2022,7 @@
         <xdr:cNvPr id="32" name="TextBox 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED41DD03-5DE8-4B11-8C7F-8B7AC8AC78A2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED41DD03-5DE8-4B11-8C7F-8B7AC8AC78A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2101,7 +2095,7 @@
         <xdr:cNvPr id="33" name="TextBox 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{511BDC1B-4ED7-4F0E-990B-D069AD8EB58A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{511BDC1B-4ED7-4F0E-990B-D069AD8EB58A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2174,7 +2168,7 @@
         <xdr:cNvPr id="34" name="TextBox 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9720E9D7-F214-4A52-A506-B80D95DF166F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9720E9D7-F214-4A52-A506-B80D95DF166F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2247,7 +2241,7 @@
         <xdr:cNvPr id="35" name="TextBox 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0697C8C0-4097-4DA6-A484-9221FD13C4F8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0697C8C0-4097-4DA6-A484-9221FD13C4F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2320,7 +2314,7 @@
         <xdr:cNvPr id="36" name="TextBox 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8385F5B5-2401-45DC-9D7E-3A38DF06D986}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8385F5B5-2401-45DC-9D7E-3A38DF06D986}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2667,247 +2661,262 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C3EA2C-4DB6-494E-AC58-8B90E6F535D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="I1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+      <c r="D3" s="5">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5">
+        <v>51</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="9">
+        <v>10100</v>
+      </c>
+      <c r="K3" s="9">
+        <v>10011</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="9">
+        <v>10010</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="I1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="7">
-        <v>20</v>
-      </c>
-      <c r="D3" s="7">
-        <v>19</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>18</v>
-      </c>
-      <c r="G3" s="7">
-        <v>51</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="6">
-        <v>10100</v>
-      </c>
-      <c r="K3" s="6">
-        <v>10011</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="6">
-        <v>10010</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
-        <v>32</v>
-      </c>
-      <c r="C6" s="7">
-        <v>7</v>
-      </c>
-      <c r="D6" s="7">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>51</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="G8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="9"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
@@ -2921,21 +2930,6 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.pic/Other/rv32i/example_instr_code.xlsx
+++ b/.pic/Other/rv32i/example_instr_code.xlsx
@@ -80,15 +80,6 @@
     <t>0100 000</t>
   </si>
   <si>
-    <t>7 бит</t>
-  </si>
-  <si>
-    <t>5 бит</t>
-  </si>
-  <si>
-    <t>3 бита</t>
-  </si>
-  <si>
     <t>(0x01498933)</t>
   </si>
   <si>
@@ -102,6 +93,15 @@
   </si>
   <si>
     <t>Machine code</t>
+  </si>
+  <si>
+    <t>3 bits</t>
+  </si>
+  <si>
+    <t>5 bits</t>
+  </si>
+  <si>
+    <t>7 bits</t>
   </si>
 </sst>
 </file>
@@ -220,8 +220,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,10 +232,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -275,7 +275,7 @@
         <xdr:cNvPr id="3" name="Правая круглая скобка 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8AD72D32-776C-4736-B66D-3CCAFD71C033}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AD72D32-776C-4736-B66D-3CCAFD71C033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -334,7 +334,7 @@
         <xdr:cNvPr id="4" name="Правая круглая скобка 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4613D476-DBFD-46EB-B0AB-B50870D03C20}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4613D476-DBFD-46EB-B0AB-B50870D03C20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -393,7 +393,7 @@
         <xdr:cNvPr id="5" name="Правая круглая скобка 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2CAAEAE2-7C9A-4A0F-A01F-37161E90E4E1}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CAAEAE2-7C9A-4A0F-A01F-37161E90E4E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -452,7 +452,7 @@
         <xdr:cNvPr id="6" name="Правая круглая скобка 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5B727BC8-F5A5-4892-9F3A-471622832A53}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B727BC8-F5A5-4892-9F3A-471622832A53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -511,7 +511,7 @@
         <xdr:cNvPr id="7" name="Правая круглая скобка 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2A3379B5-B194-4E2D-8A30-35AA3E27FF03}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A3379B5-B194-4E2D-8A30-35AA3E27FF03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -570,7 +570,7 @@
         <xdr:cNvPr id="9" name="Правая круглая скобка 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9D711405-87A4-444D-AE01-1F3708710AB4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D711405-87A4-444D-AE01-1F3708710AB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -629,7 +629,7 @@
         <xdr:cNvPr id="10" name="Правая круглая скобка 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4D2E2EF2-0404-459A-BCA9-0D0BD586D977}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E2EF2-0404-459A-BCA9-0D0BD586D977}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -688,7 +688,7 @@
         <xdr:cNvPr id="11" name="Правая круглая скобка 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{2072E865-8694-4852-8E9B-020338661E57}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072E865-8694-4852-8E9B-020338661E57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -747,7 +747,7 @@
         <xdr:cNvPr id="13" name="Правая круглая скобка 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0684CE70-7DDC-4530-9AFE-2DD98F1096A5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0684CE70-7DDC-4530-9AFE-2DD98F1096A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -806,7 +806,7 @@
         <xdr:cNvPr id="14" name="Правая круглая скобка 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0E8BB5D8-667B-4A9F-B14F-42853C233854}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E8BB5D8-667B-4A9F-B14F-42853C233854}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -865,7 +865,7 @@
         <xdr:cNvPr id="15" name="Правая круглая скобка 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6FC60ACD-2584-476E-A503-82676D64B353}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC60ACD-2584-476E-A503-82676D64B353}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -924,7 +924,7 @@
         <xdr:cNvPr id="16" name="Правая круглая скобка 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E2AB13F0-762C-4879-AFD3-4CE2A7F213B4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2AB13F0-762C-4879-AFD3-4CE2A7F213B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -983,7 +983,7 @@
         <xdr:cNvPr id="17" name="Правая круглая скобка 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3F860691-8868-4774-B441-248AD237CFD2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F860691-8868-4774-B441-248AD237CFD2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1042,7 +1042,7 @@
         <xdr:cNvPr id="18" name="Правая круглая скобка 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B9F9CB1D-6C2E-44D9-B66A-4111848A6BC7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F9CB1D-6C2E-44D9-B66A-4111848A6BC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1101,7 +1101,7 @@
         <xdr:cNvPr id="19" name="Правая круглая скобка 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5508713C-AEAF-4B62-88AA-3653ABAD411A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5508713C-AEAF-4B62-88AA-3653ABAD411A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1160,7 +1160,7 @@
         <xdr:cNvPr id="20" name="Правая круглая скобка 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{155D0124-2059-4D4D-99E2-719AB9D8CA16}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{155D0124-2059-4D4D-99E2-719AB9D8CA16}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1219,7 +1219,7 @@
         <xdr:cNvPr id="21" name="TextBox 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{56D05A31-49FC-466E-BA5A-B5D0634DA844}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D05A31-49FC-466E-BA5A-B5D0634DA844}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1292,7 +1292,7 @@
         <xdr:cNvPr id="22" name="TextBox 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FB09DC36-352C-424A-B6B8-A49A3F14C290}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB09DC36-352C-424A-B6B8-A49A3F14C290}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1365,7 +1365,7 @@
         <xdr:cNvPr id="23" name="TextBox 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CDFCD283-19D7-4AC1-9D14-5DD08D2C094D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDFCD283-19D7-4AC1-9D14-5DD08D2C094D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1438,7 +1438,7 @@
         <xdr:cNvPr id="24" name="TextBox 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{34889B57-E1E9-44B4-8491-F6CAF2E16A96}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34889B57-E1E9-44B4-8491-F6CAF2E16A96}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1511,7 +1511,7 @@
         <xdr:cNvPr id="25" name="TextBox 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1B1FDA8A-5ABE-460A-AC29-4D1D633C1CD4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B1FDA8A-5ABE-460A-AC29-4D1D633C1CD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1584,7 +1584,7 @@
         <xdr:cNvPr id="26" name="TextBox 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{FE450EE7-CB30-4B4E-9392-A28450621293}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE450EE7-CB30-4B4E-9392-A28450621293}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1657,7 +1657,7 @@
         <xdr:cNvPr id="27" name="TextBox 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BAB4829E-DE9A-4743-B5F2-D416BF1B0AC7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAB4829E-DE9A-4743-B5F2-D416BF1B0AC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1730,7 +1730,7 @@
         <xdr:cNvPr id="28" name="TextBox 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7C630E6C-77F1-47B9-AC8E-14ECD5BD5BCB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C630E6C-77F1-47B9-AC8E-14ECD5BD5BCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1803,7 +1803,7 @@
         <xdr:cNvPr id="29" name="TextBox 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{59381342-04B7-46B1-9626-D25F082ED2F4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59381342-04B7-46B1-9626-D25F082ED2F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1876,7 +1876,7 @@
         <xdr:cNvPr id="30" name="TextBox 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{265F17FE-BCA8-458B-9AE4-D9337C8557C5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265F17FE-BCA8-458B-9AE4-D9337C8557C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1949,7 +1949,7 @@
         <xdr:cNvPr id="31" name="TextBox 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D452D1CC-A63D-4E5D-8484-D2C73EC183EC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D452D1CC-A63D-4E5D-8484-D2C73EC183EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2022,7 +2022,7 @@
         <xdr:cNvPr id="32" name="TextBox 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED41DD03-5DE8-4B11-8C7F-8B7AC8AC78A2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED41DD03-5DE8-4B11-8C7F-8B7AC8AC78A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2095,7 +2095,7 @@
         <xdr:cNvPr id="33" name="TextBox 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{511BDC1B-4ED7-4F0E-990B-D069AD8EB58A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{511BDC1B-4ED7-4F0E-990B-D069AD8EB58A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2168,7 +2168,7 @@
         <xdr:cNvPr id="34" name="TextBox 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9720E9D7-F214-4A52-A506-B80D95DF166F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9720E9D7-F214-4A52-A506-B80D95DF166F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2241,7 +2241,7 @@
         <xdr:cNvPr id="35" name="TextBox 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0697C8C0-4097-4DA6-A484-9221FD13C4F8}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0697C8C0-4097-4DA6-A484-9221FD13C4F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2314,7 +2314,7 @@
         <xdr:cNvPr id="36" name="TextBox 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{8385F5B5-2401-45DC-9D7E-3A38DF06D986}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8385F5B5-2401-45DC-9D7E-3A38DF06D986}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2661,7 +2661,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2679,24 +2679,24 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="I1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="I1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
     </row>
     <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2758,26 +2758,26 @@
       <c r="G3" s="5">
         <v>51</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>10100</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="8">
         <v>10011</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="8">
         <v>10010</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="8" t="s">
         <v>14</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -2790,12 +2790,12 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
       <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2839,8 +2839,8 @@
       <c r="N6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>22</v>
+      <c r="O6" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -2859,64 +2859,49 @@
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="4"/>
+      <c r="O7" s="9"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="I1:N1"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="I3:I4"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
@@ -2930,6 +2915,21 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="I1:N1"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.pic/Other/rv32i/example_instr_code.xlsx
+++ b/.pic/Other/rv32i/example_instr_code.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\voult\Desktop\APS-reborn\.pic\Other\rv32i\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE47DEEE-8362-410D-B139-02CAD8AFDE58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{11EFC6F1-332B-4EA5-A40A-5D79FF20EEEF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,15 +25,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
-  <si>
-    <t>Код ассемблера</t>
-  </si>
-  <si>
-    <t>Значения полей</t>
-  </si>
-  <si>
-    <t>Машинный код</t>
-  </si>
   <si>
     <t>add s2, s3, s4</t>
   </si>
@@ -95,25 +80,34 @@
     <t>0100 000</t>
   </si>
   <si>
-    <t>7 бит</t>
-  </si>
-  <si>
-    <t>5 бит</t>
-  </si>
-  <si>
-    <t>3 бита</t>
-  </si>
-  <si>
     <t>(0x01498933)</t>
   </si>
   <si>
     <t>(0x407302B3)</t>
   </si>
+  <si>
+    <t>Assembly code</t>
+  </si>
+  <si>
+    <t>Field values</t>
+  </si>
+  <si>
+    <t>Machine code</t>
+  </si>
+  <si>
+    <t>3 bits</t>
+  </si>
+  <si>
+    <t>5 bits</t>
+  </si>
+  <si>
+    <t>7 bits</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -224,21 +218,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -281,7 +275,7 @@
         <xdr:cNvPr id="3" name="Правая круглая скобка 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AD72D32-776C-4736-B66D-3CCAFD71C033}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AD72D32-776C-4736-B66D-3CCAFD71C033}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -340,7 +334,7 @@
         <xdr:cNvPr id="4" name="Правая круглая скобка 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4613D476-DBFD-46EB-B0AB-B50870D03C20}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4613D476-DBFD-46EB-B0AB-B50870D03C20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -399,7 +393,7 @@
         <xdr:cNvPr id="5" name="Правая круглая скобка 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CAAEAE2-7C9A-4A0F-A01F-37161E90E4E1}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CAAEAE2-7C9A-4A0F-A01F-37161E90E4E1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -458,7 +452,7 @@
         <xdr:cNvPr id="6" name="Правая круглая скобка 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B727BC8-F5A5-4892-9F3A-471622832A53}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B727BC8-F5A5-4892-9F3A-471622832A53}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -517,7 +511,7 @@
         <xdr:cNvPr id="7" name="Правая круглая скобка 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A3379B5-B194-4E2D-8A30-35AA3E27FF03}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A3379B5-B194-4E2D-8A30-35AA3E27FF03}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -576,7 +570,7 @@
         <xdr:cNvPr id="9" name="Правая круглая скобка 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D711405-87A4-444D-AE01-1F3708710AB4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D711405-87A4-444D-AE01-1F3708710AB4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -635,7 +629,7 @@
         <xdr:cNvPr id="10" name="Правая круглая скобка 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E2EF2-0404-459A-BCA9-0D0BD586D977}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D2E2EF2-0404-459A-BCA9-0D0BD586D977}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -694,7 +688,7 @@
         <xdr:cNvPr id="11" name="Правая круглая скобка 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072E865-8694-4852-8E9B-020338661E57}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072E865-8694-4852-8E9B-020338661E57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -753,7 +747,7 @@
         <xdr:cNvPr id="13" name="Правая круглая скобка 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0684CE70-7DDC-4530-9AFE-2DD98F1096A5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0684CE70-7DDC-4530-9AFE-2DD98F1096A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -812,7 +806,7 @@
         <xdr:cNvPr id="14" name="Правая круглая скобка 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E8BB5D8-667B-4A9F-B14F-42853C233854}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E8BB5D8-667B-4A9F-B14F-42853C233854}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -871,7 +865,7 @@
         <xdr:cNvPr id="15" name="Правая круглая скобка 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC60ACD-2584-476E-A503-82676D64B353}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC60ACD-2584-476E-A503-82676D64B353}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -930,7 +924,7 @@
         <xdr:cNvPr id="16" name="Правая круглая скобка 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2AB13F0-762C-4879-AFD3-4CE2A7F213B4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2AB13F0-762C-4879-AFD3-4CE2A7F213B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -989,7 +983,7 @@
         <xdr:cNvPr id="17" name="Правая круглая скобка 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F860691-8868-4774-B441-248AD237CFD2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F860691-8868-4774-B441-248AD237CFD2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1048,7 +1042,7 @@
         <xdr:cNvPr id="18" name="Правая круглая скобка 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F9CB1D-6C2E-44D9-B66A-4111848A6BC7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F9CB1D-6C2E-44D9-B66A-4111848A6BC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1107,7 +1101,7 @@
         <xdr:cNvPr id="19" name="Правая круглая скобка 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5508713C-AEAF-4B62-88AA-3653ABAD411A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5508713C-AEAF-4B62-88AA-3653ABAD411A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1166,7 +1160,7 @@
         <xdr:cNvPr id="20" name="Правая круглая скобка 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{155D0124-2059-4D4D-99E2-719AB9D8CA16}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{155D0124-2059-4D4D-99E2-719AB9D8CA16}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1225,7 +1219,7 @@
         <xdr:cNvPr id="21" name="TextBox 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D05A31-49FC-466E-BA5A-B5D0634DA844}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56D05A31-49FC-466E-BA5A-B5D0634DA844}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1298,7 +1292,7 @@
         <xdr:cNvPr id="22" name="TextBox 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB09DC36-352C-424A-B6B8-A49A3F14C290}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB09DC36-352C-424A-B6B8-A49A3F14C290}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,7 +1365,7 @@
         <xdr:cNvPr id="23" name="TextBox 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDFCD283-19D7-4AC1-9D14-5DD08D2C094D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDFCD283-19D7-4AC1-9D14-5DD08D2C094D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1444,7 +1438,7 @@
         <xdr:cNvPr id="24" name="TextBox 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34889B57-E1E9-44B4-8491-F6CAF2E16A96}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34889B57-E1E9-44B4-8491-F6CAF2E16A96}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1517,7 +1511,7 @@
         <xdr:cNvPr id="25" name="TextBox 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B1FDA8A-5ABE-460A-AC29-4D1D633C1CD4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B1FDA8A-5ABE-460A-AC29-4D1D633C1CD4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1590,7 +1584,7 @@
         <xdr:cNvPr id="26" name="TextBox 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE450EE7-CB30-4B4E-9392-A28450621293}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE450EE7-CB30-4B4E-9392-A28450621293}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1663,7 +1657,7 @@
         <xdr:cNvPr id="27" name="TextBox 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAB4829E-DE9A-4743-B5F2-D416BF1B0AC7}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAB4829E-DE9A-4743-B5F2-D416BF1B0AC7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1736,7 +1730,7 @@
         <xdr:cNvPr id="28" name="TextBox 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C630E6C-77F1-47B9-AC8E-14ECD5BD5BCB}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C630E6C-77F1-47B9-AC8E-14ECD5BD5BCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1809,7 +1803,7 @@
         <xdr:cNvPr id="29" name="TextBox 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59381342-04B7-46B1-9626-D25F082ED2F4}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59381342-04B7-46B1-9626-D25F082ED2F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1882,7 +1876,7 @@
         <xdr:cNvPr id="30" name="TextBox 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265F17FE-BCA8-458B-9AE4-D9337C8557C5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265F17FE-BCA8-458B-9AE4-D9337C8557C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1955,7 +1949,7 @@
         <xdr:cNvPr id="31" name="TextBox 30">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D452D1CC-A63D-4E5D-8484-D2C73EC183EC}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D452D1CC-A63D-4E5D-8484-D2C73EC183EC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2028,7 +2022,7 @@
         <xdr:cNvPr id="32" name="TextBox 31">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED41DD03-5DE8-4B11-8C7F-8B7AC8AC78A2}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED41DD03-5DE8-4B11-8C7F-8B7AC8AC78A2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2101,7 +2095,7 @@
         <xdr:cNvPr id="33" name="TextBox 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{511BDC1B-4ED7-4F0E-990B-D069AD8EB58A}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{511BDC1B-4ED7-4F0E-990B-D069AD8EB58A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2174,7 +2168,7 @@
         <xdr:cNvPr id="34" name="TextBox 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9720E9D7-F214-4A52-A506-B80D95DF166F}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9720E9D7-F214-4A52-A506-B80D95DF166F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2247,7 +2241,7 @@
         <xdr:cNvPr id="35" name="TextBox 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0697C8C0-4097-4DA6-A484-9221FD13C4F8}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0697C8C0-4097-4DA6-A484-9221FD13C4F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2320,7 +2314,7 @@
         <xdr:cNvPr id="36" name="TextBox 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8385F5B5-2401-45DC-9D7E-3A38DF06D986}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8385F5B5-2401-45DC-9D7E-3A38DF06D986}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2667,243 +2661,243 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C3EA2C-4DB6-494E-AC58-8B90E6F535D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" customWidth="1"/>
+    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="I1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+      <c r="D3" s="5">
+        <v>19</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5">
+        <v>51</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="8">
+        <v>10100</v>
+      </c>
+      <c r="K3" s="8">
+        <v>10011</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="8">
+        <v>10010</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="I1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="7">
-        <v>20</v>
-      </c>
-      <c r="D3" s="7">
-        <v>19</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>18</v>
-      </c>
-      <c r="G3" s="7">
-        <v>51</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="6">
-        <v>10100</v>
-      </c>
-      <c r="K3" s="6">
-        <v>10011</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="6">
-        <v>10010</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5">
+        <v>7</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
-        <v>32</v>
-      </c>
-      <c r="C6" s="7">
-        <v>7</v>
-      </c>
-      <c r="D6" s="7">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <v>5</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>51</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" s="9" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
       <c r="O7" s="9"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2928,6 +2922,7 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
+    <mergeCell ref="I3:I4"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
@@ -2935,7 +2930,6 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
-    <mergeCell ref="I3:I4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
